--- a/contracts/ChainSwap/output_debug/storage_semantic.xlsx
+++ b/contracts/ChainSwap/output_debug/storage_semantic.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,15 +441,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>semantic_with_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>var_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>slot_Offset</t>
         </is>
@@ -466,15 +471,20 @@
           <t>stor_0_0_0</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bool stor_0_0_0</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>0x0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>bytes 0 to 0</t>
         </is>
@@ -491,15 +501,20 @@
           <t>___TokenMapped_init</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bool ___TokenMapped_init</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0x0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>bytes 1 to 1</t>
         </is>
@@ -516,15 +531,20 @@
           <t>_dOMAIN_SEPARATOR</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bytes32 _dOMAIN_SEPARATOR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0x65</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -541,15 +561,20 @@
           <t>_mainChainId</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>uint256 _mainChainId</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>0x67</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -566,15 +591,20 @@
           <t>_authQuotaOf</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mapping (address =&gt; uint256) _authQuotaOf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>0x6a</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -591,15 +621,20 @@
           <t>_sentCount</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mapping (uint256 =&gt; mapping (address =&gt; uint256)) _sentCount</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0x6b</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -616,15 +651,20 @@
           <t>_sent</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mapping (uint256 =&gt; mapping (address =&gt; mapping (uint256 =&gt; uint256))) _sent</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0x6c</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -641,15 +681,20 @@
           <t>_received</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mapping (uint256 =&gt; mapping (address =&gt; mapping (uint256 =&gt; uint256))) _received</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>0x6d</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>bytes 0 to 31</t>
         </is>
@@ -666,15 +711,20 @@
           <t>_factory</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>address _factory</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>0x66</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>bytes 0 to 19</t>
         </is>
@@ -691,15 +741,20 @@
           <t>_token</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>address _token</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>0x68</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>bytes 0 to 19</t>
         </is>
@@ -716,15 +771,20 @@
           <t>_creator</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>address _creator</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>bytes 0 to 19</t>
         </is>
